--- a/Team-Data/2015-16/4-4-2015-16.xlsx
+++ b/Team-Data/2015-16/4-4-2015-16.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E2" t="n">
         <v>45</v>
       </c>
       <c r="F2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G2" t="n">
-        <v>0.592</v>
+        <v>0.584</v>
       </c>
       <c r="H2" t="n">
         <v>48.4</v>
@@ -688,16 +755,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.35</v>
+        <v>0.349</v>
       </c>
       <c r="O2" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="P2" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="Q2" t="n">
         <v>0.786</v>
@@ -712,7 +779,7 @@
         <v>41.9</v>
       </c>
       <c r="U2" t="n">
-        <v>25.7</v>
+        <v>25.6</v>
       </c>
       <c r="V2" t="n">
         <v>14.8</v>
@@ -721,22 +788,22 @@
         <v>9</v>
       </c>
       <c r="X2" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Y2" t="n">
         <v>5.1</v>
       </c>
       <c r="Z2" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="AA2" t="n">
         <v>18.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>103</v>
+        <v>102.9</v>
       </c>
       <c r="AC2" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AD2" t="n">
         <v>4</v>
@@ -751,16 +818,16 @@
         <v>7</v>
       </c>
       <c r="AH2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI2" t="n">
         <v>8</v>
       </c>
       <c r="AJ2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL2" t="n">
         <v>6</v>
@@ -772,13 +839,13 @@
         <v>16</v>
       </c>
       <c r="AO2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP2" t="n">
         <v>29</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AR2" t="n">
         <v>30</v>
@@ -787,7 +854,7 @@
         <v>14</v>
       </c>
       <c r="AT2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU2" t="n">
         <v>2</v>
@@ -796,25 +863,25 @@
         <v>19</v>
       </c>
       <c r="AW2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX2" t="n">
         <v>7</v>
       </c>
       <c r="AY2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ2" t="n">
         <v>6</v>
       </c>
       <c r="BA2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB2" t="n">
         <v>12</v>
       </c>
       <c r="BC2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-4-2015-16</t>
+          <t>2016-04-04</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F3" t="n">
         <v>32</v>
       </c>
       <c r="G3" t="n">
-        <v>0.579</v>
+        <v>0.584</v>
       </c>
       <c r="H3" t="n">
         <v>48.3</v>
@@ -870,19 +937,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="N3" t="n">
         <v>0.334</v>
       </c>
       <c r="O3" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="P3" t="n">
         <v>23.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.785</v>
+        <v>0.788</v>
       </c>
       <c r="R3" t="n">
         <v>11.8</v>
@@ -891,19 +958,19 @@
         <v>33.5</v>
       </c>
       <c r="T3" t="n">
-        <v>45.3</v>
+        <v>45.2</v>
       </c>
       <c r="U3" t="n">
         <v>24.1</v>
       </c>
       <c r="V3" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="X3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y3" t="n">
         <v>5.4</v>
@@ -915,34 +982,34 @@
         <v>20.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>105.6</v>
+        <v>105.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AD3" t="n">
         <v>4</v>
       </c>
       <c r="AE3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AG3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AH3" t="n">
         <v>24</v>
       </c>
       <c r="AI3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ3" t="n">
         <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL3" t="n">
         <v>12</v>
@@ -957,10 +1024,10 @@
         <v>11</v>
       </c>
       <c r="AP3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR3" t="n">
         <v>3</v>
@@ -975,7 +1042,7 @@
         <v>6</v>
       </c>
       <c r="AV3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW3" t="n">
         <v>2</v>
@@ -984,7 +1051,7 @@
         <v>24</v>
       </c>
       <c r="AY3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ3" t="n">
         <v>28</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-4-2015-16</t>
+          <t>2016-04-04</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E4" t="n">
         <v>21</v>
       </c>
       <c r="F4" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G4" t="n">
-        <v>0.276</v>
+        <v>0.273</v>
       </c>
       <c r="H4" t="n">
         <v>48.2</v>
@@ -1043,31 +1110,31 @@
         <v>38.2</v>
       </c>
       <c r="J4" t="n">
-        <v>83.8</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L4" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="M4" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="N4" t="n">
-        <v>0.352</v>
+        <v>0.35</v>
       </c>
       <c r="O4" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="P4" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="Q4" t="n">
         <v>0.761</v>
       </c>
       <c r="R4" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="S4" t="n">
         <v>32.1</v>
@@ -1076,13 +1143,13 @@
         <v>42.5</v>
       </c>
       <c r="U4" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="V4" t="n">
         <v>15</v>
       </c>
       <c r="W4" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X4" t="n">
         <v>3.9</v>
@@ -1094,13 +1161,13 @@
         <v>18</v>
       </c>
       <c r="AA4" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="AB4" t="n">
         <v>98.40000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>-6.8</v>
+        <v>-6.9</v>
       </c>
       <c r="AD4" t="n">
         <v>4</v>
@@ -1118,10 +1185,10 @@
         <v>26</v>
       </c>
       <c r="AI4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK4" t="n">
         <v>12</v>
@@ -1136,13 +1203,13 @@
         <v>14</v>
       </c>
       <c r="AO4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP4" t="n">
         <v>27</v>
       </c>
       <c r="AQ4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR4" t="n">
         <v>15</v>
@@ -1175,7 +1242,7 @@
         <v>28</v>
       </c>
       <c r="BB4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC4" t="n">
         <v>27</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-4-2015-16</t>
+          <t>2016-04-04</t>
         </is>
       </c>
     </row>
@@ -1207,58 +1274,58 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E5" t="n">
         <v>44</v>
       </c>
       <c r="F5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G5" t="n">
-        <v>0.587</v>
+        <v>0.579</v>
       </c>
       <c r="H5" t="n">
         <v>48.5</v>
       </c>
       <c r="I5" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J5" t="n">
         <v>84.40000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.438</v>
+        <v>0.437</v>
       </c>
       <c r="L5" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="M5" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="N5" t="n">
-        <v>0.361</v>
+        <v>0.36</v>
       </c>
       <c r="O5" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="P5" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="Q5" t="n">
         <v>0.79</v>
       </c>
       <c r="R5" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="S5" t="n">
-        <v>35.1</v>
+        <v>35</v>
       </c>
       <c r="T5" t="n">
         <v>44</v>
       </c>
       <c r="U5" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="V5" t="n">
         <v>12.7</v>
@@ -1267,7 +1334,7 @@
         <v>7.2</v>
       </c>
       <c r="X5" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Y5" t="n">
         <v>5.5</v>
@@ -1276,25 +1343,25 @@
         <v>18.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>103.2</v>
+        <v>103.1</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AE5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF5" t="n">
         <v>7</v>
       </c>
       <c r="AG5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH5" t="n">
         <v>6</v>
@@ -1303,7 +1370,7 @@
         <v>24</v>
       </c>
       <c r="AJ5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK5" t="n">
         <v>27</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-4-2015-16</t>
+          <t>2016-04-04</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E6" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F6" t="n">
         <v>38</v>
       </c>
       <c r="G6" t="n">
-        <v>0.493</v>
+        <v>0.506</v>
       </c>
       <c r="H6" t="n">
         <v>48.6</v>
@@ -1407,43 +1474,43 @@
         <v>38.6</v>
       </c>
       <c r="J6" t="n">
-        <v>88</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.438</v>
+        <v>0.439</v>
       </c>
       <c r="L6" t="n">
         <v>7.8</v>
       </c>
       <c r="M6" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0.366</v>
+        <v>0.369</v>
       </c>
       <c r="O6" t="n">
         <v>16.3</v>
       </c>
       <c r="P6" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.785</v>
+        <v>0.784</v>
       </c>
       <c r="R6" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="S6" t="n">
-        <v>35.4</v>
+        <v>35.5</v>
       </c>
       <c r="T6" t="n">
-        <v>46.6</v>
+        <v>46.5</v>
       </c>
       <c r="U6" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="V6" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W6" t="n">
         <v>6</v>
@@ -1455,28 +1522,28 @@
         <v>5.8</v>
       </c>
       <c r="Z6" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AA6" t="n">
         <v>18.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>101.2</v>
+        <v>101.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>-1.8</v>
+        <v>-1.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="AE6" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AF6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG6" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AH6" t="n">
         <v>3</v>
@@ -1488,10 +1555,10 @@
         <v>2</v>
       </c>
       <c r="AK6" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM6" t="n">
         <v>24</v>
@@ -1500,7 +1567,7 @@
         <v>5</v>
       </c>
       <c r="AO6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP6" t="n">
         <v>26</v>
@@ -1512,16 +1579,16 @@
         <v>8</v>
       </c>
       <c r="AS6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT6" t="n">
         <v>2</v>
       </c>
       <c r="AU6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW6" t="n">
         <v>29</v>
@@ -1536,13 +1603,13 @@
         <v>5</v>
       </c>
       <c r="BA6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB6" t="n">
         <v>21</v>
       </c>
       <c r="BC6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-4-2015-16</t>
+          <t>2016-04-04</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E7" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G7" t="n">
-        <v>0.72</v>
+        <v>0.714</v>
       </c>
       <c r="H7" t="n">
         <v>48.4</v>
@@ -1589,10 +1656,10 @@
         <v>38.6</v>
       </c>
       <c r="J7" t="n">
-        <v>84</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.46</v>
+        <v>0.459</v>
       </c>
       <c r="L7" t="n">
         <v>10.6</v>
@@ -1601,28 +1668,28 @@
         <v>29.6</v>
       </c>
       <c r="N7" t="n">
-        <v>0.358</v>
+        <v>0.359</v>
       </c>
       <c r="O7" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="P7" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.746</v>
+        <v>0.743</v>
       </c>
       <c r="R7" t="n">
         <v>10.8</v>
       </c>
       <c r="S7" t="n">
-        <v>33.7</v>
+        <v>33.9</v>
       </c>
       <c r="T7" t="n">
-        <v>44.5</v>
+        <v>44.7</v>
       </c>
       <c r="U7" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="V7" t="n">
         <v>13.6</v>
@@ -1631,25 +1698,25 @@
         <v>6.8</v>
       </c>
       <c r="X7" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>104.2</v>
+        <v>104.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="AE7" t="n">
         <v>3</v>
@@ -1661,7 +1728,7 @@
         <v>3</v>
       </c>
       <c r="AH7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI7" t="n">
         <v>9</v>
@@ -1673,40 +1740,40 @@
         <v>9</v>
       </c>
       <c r="AL7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM7" t="n">
         <v>3</v>
       </c>
       <c r="AN7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AO7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AP7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ7" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AR7" t="n">
         <v>11</v>
       </c>
       <c r="AS7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AT7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX7" t="n">
         <v>28</v>
@@ -1721,7 +1788,7 @@
         <v>12</v>
       </c>
       <c r="BB7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC7" t="n">
         <v>4</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-4-2015-16</t>
+          <t>2016-04-04</t>
         </is>
       </c>
     </row>
@@ -1753,19 +1820,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E8" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F8" t="n">
         <v>38</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5</v>
+        <v>0.506</v>
       </c>
       <c r="H8" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="I8" t="n">
         <v>37.7</v>
@@ -1780,34 +1847,34 @@
         <v>9.800000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>28.4</v>
+        <v>28.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0.345</v>
+        <v>0.346</v>
       </c>
       <c r="O8" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="P8" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.797</v>
+        <v>0.795</v>
       </c>
       <c r="R8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>33.8</v>
+        <v>33.9</v>
       </c>
       <c r="T8" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
       <c r="U8" t="n">
         <v>22.3</v>
       </c>
       <c r="V8" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="W8" t="n">
         <v>6.8</v>
@@ -1819,28 +1886,28 @@
         <v>4.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>102.7</v>
+        <v>102.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.7</v>
+        <v>-0.4</v>
       </c>
       <c r="AD8" t="n">
         <v>4</v>
       </c>
       <c r="AE8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH8" t="n">
         <v>1</v>
@@ -1855,19 +1922,19 @@
         <v>20</v>
       </c>
       <c r="AL8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AM8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO8" t="n">
         <v>12</v>
       </c>
       <c r="AP8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ8" t="n">
         <v>3</v>
@@ -1876,10 +1943,10 @@
         <v>26</v>
       </c>
       <c r="AS8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AT8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU8" t="n">
         <v>15</v>
@@ -1888,25 +1955,25 @@
         <v>2</v>
       </c>
       <c r="AW8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX8" t="n">
         <v>29</v>
       </c>
       <c r="AY8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ8" t="n">
         <v>8</v>
       </c>
       <c r="BA8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB8" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC8" t="n">
         <v>15</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>16</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-4-2015-16</t>
+          <t>2016-04-04</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E9" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F9" t="n">
         <v>46</v>
       </c>
       <c r="G9" t="n">
-        <v>0.403</v>
+        <v>0.41</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
@@ -1953,7 +2020,7 @@
         <v>37.7</v>
       </c>
       <c r="J9" t="n">
-        <v>85.40000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="K9" t="n">
         <v>0.442</v>
@@ -1962,67 +2029,67 @@
         <v>8</v>
       </c>
       <c r="M9" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="N9" t="n">
-        <v>0.339</v>
+        <v>0.341</v>
       </c>
       <c r="O9" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="P9" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.769</v>
+        <v>0.768</v>
       </c>
       <c r="R9" t="n">
         <v>11.5</v>
       </c>
       <c r="S9" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="T9" t="n">
         <v>44.6</v>
       </c>
       <c r="U9" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="V9" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W9" t="n">
         <v>7.4</v>
       </c>
       <c r="X9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AA9" t="n">
         <v>21.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>102.1</v>
+        <v>102.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>-3</v>
+        <v>-2.7</v>
       </c>
       <c r="AD9" t="n">
         <v>1</v>
       </c>
       <c r="AE9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF9" t="n">
         <v>22</v>
       </c>
-      <c r="AF9" t="n">
-        <v>24</v>
-      </c>
       <c r="AG9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH9" t="n">
         <v>15</v>
@@ -2034,13 +2101,13 @@
         <v>11</v>
       </c>
       <c r="AK9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL9" t="n">
         <v>18</v>
       </c>
       <c r="AM9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN9" t="n">
         <v>24</v>
@@ -2055,13 +2122,13 @@
         <v>14</v>
       </c>
       <c r="AR9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AS9" t="n">
         <v>19</v>
       </c>
       <c r="AT9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU9" t="n">
         <v>14</v>
@@ -2088,7 +2155,7 @@
         <v>16</v>
       </c>
       <c r="BC9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-4-2015-16</t>
+          <t>2016-04-04</t>
         </is>
       </c>
     </row>
@@ -2117,28 +2184,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E10" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F10" t="n">
         <v>36</v>
       </c>
       <c r="G10" t="n">
-        <v>0.52</v>
+        <v>0.532</v>
       </c>
       <c r="H10" t="n">
         <v>48.5</v>
       </c>
       <c r="I10" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J10" t="n">
         <v>86.7</v>
       </c>
       <c r="K10" t="n">
-        <v>0.441</v>
+        <v>0.439</v>
       </c>
       <c r="L10" t="n">
         <v>8.9</v>
@@ -2147,25 +2214,25 @@
         <v>26.2</v>
       </c>
       <c r="N10" t="n">
-        <v>0.34</v>
+        <v>0.342</v>
       </c>
       <c r="O10" t="n">
-        <v>16.6</v>
+        <v>16.8</v>
       </c>
       <c r="P10" t="n">
-        <v>25.2</v>
+        <v>25.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.659</v>
+        <v>0.662</v>
       </c>
       <c r="R10" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="S10" t="n">
-        <v>33.8</v>
+        <v>33.9</v>
       </c>
       <c r="T10" t="n">
-        <v>46.3</v>
+        <v>46.4</v>
       </c>
       <c r="U10" t="n">
         <v>19.5</v>
@@ -2174,7 +2241,7 @@
         <v>13.6</v>
       </c>
       <c r="W10" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X10" t="n">
         <v>3.6</v>
@@ -2186,37 +2253,37 @@
         <v>19.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>102</v>
+        <v>101.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="AE10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AF10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AG10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI10" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AJ10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL10" t="n">
         <v>11</v>
@@ -2240,7 +2307,7 @@
         <v>2</v>
       </c>
       <c r="AS10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT10" t="n">
         <v>3</v>
@@ -2267,7 +2334,7 @@
         <v>5</v>
       </c>
       <c r="BB10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC10" t="n">
         <v>13</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-4-2015-16</t>
+          <t>2016-04-04</t>
         </is>
       </c>
     </row>
@@ -2299,28 +2366,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E11" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
       </c>
       <c r="G11" t="n">
-        <v>0.895</v>
+        <v>0.896</v>
       </c>
       <c r="H11" t="n">
         <v>48.5</v>
       </c>
       <c r="I11" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="J11" t="n">
-        <v>87.3</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.488</v>
+        <v>0.487</v>
       </c>
       <c r="L11" t="n">
         <v>13.2</v>
@@ -2329,7 +2396,7 @@
         <v>31.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0.42</v>
+        <v>0.418</v>
       </c>
       <c r="O11" t="n">
         <v>17</v>
@@ -2338,16 +2405,16 @@
         <v>22.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.758</v>
+        <v>0.76</v>
       </c>
       <c r="R11" t="n">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
       <c r="S11" t="n">
         <v>36.1</v>
       </c>
       <c r="T11" t="n">
-        <v>46</v>
+        <v>46.2</v>
       </c>
       <c r="U11" t="n">
         <v>29</v>
@@ -2365,10 +2432,10 @@
         <v>4.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AB11" t="n">
         <v>115.3</v>
@@ -2389,7 +2456,7 @@
         <v>1</v>
       </c>
       <c r="AH11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI11" t="n">
         <v>1</v>
@@ -2398,7 +2465,7 @@
         <v>3</v>
       </c>
       <c r="AK11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL11" t="n">
         <v>1</v>
@@ -2419,7 +2486,7 @@
         <v>18</v>
       </c>
       <c r="AR11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS11" t="n">
         <v>1</v>
@@ -2431,7 +2498,7 @@
         <v>1</v>
       </c>
       <c r="AV11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW11" t="n">
         <v>8</v>
@@ -2440,13 +2507,13 @@
         <v>2</v>
       </c>
       <c r="AY11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB11" t="n">
         <v>1</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-4-2015-16</t>
+          <t>2016-04-04</t>
         </is>
       </c>
     </row>
@@ -2481,28 +2548,28 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E12" t="n">
         <v>38</v>
       </c>
       <c r="F12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5</v>
+        <v>0.494</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J12" t="n">
         <v>83.3</v>
       </c>
       <c r="K12" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L12" t="n">
         <v>10.6</v>
@@ -2511,22 +2578,22 @@
         <v>30.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0.345</v>
+        <v>0.344</v>
       </c>
       <c r="O12" t="n">
         <v>20.8</v>
       </c>
       <c r="P12" t="n">
-        <v>29.9</v>
+        <v>29.8</v>
       </c>
       <c r="Q12" t="n">
         <v>0.696</v>
       </c>
       <c r="R12" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="S12" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T12" t="n">
         <v>43.1</v>
@@ -2538,58 +2605,58 @@
         <v>15.9</v>
       </c>
       <c r="W12" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="X12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y12" t="n">
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="AA12" t="n">
         <v>22.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>106.3</v>
+        <v>106</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.4</v>
+        <v>-0.7</v>
       </c>
       <c r="AD12" t="n">
         <v>4</v>
       </c>
       <c r="AE12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AF12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AG12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AH12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ12" t="n">
         <v>22</v>
       </c>
       <c r="AK12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AL12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM12" t="n">
         <v>2</v>
       </c>
       <c r="AN12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO12" t="n">
         <v>3</v>
@@ -2598,7 +2665,7 @@
         <v>1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AR12" t="n">
         <v>6</v>
@@ -2607,7 +2674,7 @@
         <v>27</v>
       </c>
       <c r="AT12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU12" t="n">
         <v>18</v>
@@ -2634,7 +2701,7 @@
         <v>4</v>
       </c>
       <c r="BC12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-4-2015-16</t>
+          <t>2016-04-04</t>
         </is>
       </c>
     </row>
@@ -2663,28 +2730,28 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E13" t="n">
         <v>41</v>
       </c>
       <c r="F13" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G13" t="n">
-        <v>0.539</v>
+        <v>0.532</v>
       </c>
       <c r="H13" t="n">
         <v>48.5</v>
       </c>
       <c r="I13" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J13" t="n">
         <v>85.3</v>
       </c>
       <c r="K13" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L13" t="n">
         <v>7.9</v>
@@ -2693,52 +2760,52 @@
         <v>22.9</v>
       </c>
       <c r="N13" t="n">
-        <v>0.346</v>
+        <v>0.347</v>
       </c>
       <c r="O13" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="P13" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.762</v>
+        <v>0.763</v>
       </c>
       <c r="R13" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="S13" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="T13" t="n">
         <v>44.3</v>
       </c>
       <c r="U13" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="V13" t="n">
         <v>14.9</v>
       </c>
       <c r="W13" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="X13" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y13" t="n">
         <v>4.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AA13" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB13" t="n">
         <v>101.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AD13" t="n">
         <v>4</v>
@@ -2765,7 +2832,7 @@
         <v>19</v>
       </c>
       <c r="AL13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM13" t="n">
         <v>20</v>
@@ -2774,31 +2841,31 @@
         <v>18</v>
       </c>
       <c r="AO13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP13" t="n">
         <v>17</v>
       </c>
       <c r="AQ13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR13" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AS13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV13" t="n">
         <v>20</v>
       </c>
       <c r="AW13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX13" t="n">
         <v>16</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-4-2015-16</t>
+          <t>2016-04-04</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F14" t="n">
         <v>28</v>
       </c>
       <c r="G14" t="n">
-        <v>0.627</v>
+        <v>0.632</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
@@ -2866,16 +2933,16 @@
         <v>82.5</v>
       </c>
       <c r="K14" t="n">
-        <v>0.463</v>
+        <v>0.464</v>
       </c>
       <c r="L14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>27</v>
+        <v>26.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0.363</v>
+        <v>0.362</v>
       </c>
       <c r="O14" t="n">
         <v>18.5</v>
@@ -2923,7 +2990,7 @@
         <v>3.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AE14" t="n">
         <v>6</v>
@@ -2938,7 +3005,7 @@
         <v>16</v>
       </c>
       <c r="AI14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ14" t="n">
         <v>25</v>
@@ -2947,7 +3014,7 @@
         <v>7</v>
       </c>
       <c r="AL14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM14" t="n">
         <v>8</v>
@@ -2962,19 +3029,19 @@
         <v>4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AR14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AS14" t="n">
         <v>20</v>
       </c>
       <c r="AT14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV14" t="n">
         <v>3</v>
@@ -2998,7 +3065,7 @@
         <v>7</v>
       </c>
       <c r="BC14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-4-2015-16</t>
+          <t>2016-04-04</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E15" t="n">
         <v>16</v>
       </c>
       <c r="F15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G15" t="n">
-        <v>0.213</v>
+        <v>0.211</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
@@ -3045,7 +3112,7 @@
         <v>35.3</v>
       </c>
       <c r="J15" t="n">
-        <v>84.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="K15" t="n">
         <v>0.416</v>
@@ -3054,19 +3121,19 @@
         <v>7.8</v>
       </c>
       <c r="M15" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="N15" t="n">
-        <v>0.318</v>
+        <v>0.317</v>
       </c>
       <c r="O15" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="P15" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.773</v>
+        <v>0.775</v>
       </c>
       <c r="R15" t="n">
         <v>10.7</v>
@@ -3093,19 +3160,19 @@
         <v>5.6</v>
       </c>
       <c r="Z15" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>97.59999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="AD15" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AE15" t="n">
         <v>29</v>
@@ -3129,7 +3196,7 @@
         <v>30</v>
       </c>
       <c r="AL15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM15" t="n">
         <v>13</v>
@@ -3144,7 +3211,7 @@
         <v>9</v>
       </c>
       <c r="AQ15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR15" t="n">
         <v>12</v>
@@ -3153,7 +3220,7 @@
         <v>24</v>
       </c>
       <c r="AT15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU15" t="n">
         <v>30</v>
@@ -3168,7 +3235,7 @@
         <v>23</v>
       </c>
       <c r="AY15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AZ15" t="n">
         <v>12</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-4-2015-16</t>
+          <t>2016-04-04</t>
         </is>
       </c>
     </row>
@@ -3209,67 +3276,67 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E16" t="n">
         <v>41</v>
       </c>
       <c r="F16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G16" t="n">
-        <v>0.539</v>
+        <v>0.532</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
       </c>
       <c r="I16" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J16" t="n">
         <v>83.2</v>
       </c>
       <c r="K16" t="n">
-        <v>0.443</v>
+        <v>0.442</v>
       </c>
       <c r="L16" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="M16" t="n">
         <v>18.4</v>
       </c>
       <c r="N16" t="n">
-        <v>0.335</v>
+        <v>0.332</v>
       </c>
       <c r="O16" t="n">
         <v>19.6</v>
       </c>
       <c r="P16" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.783</v>
+        <v>0.782</v>
       </c>
       <c r="R16" t="n">
         <v>11</v>
       </c>
       <c r="S16" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="T16" t="n">
         <v>41.5</v>
       </c>
       <c r="U16" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="V16" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="W16" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="X16" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y16" t="n">
         <v>5.6</v>
@@ -3281,10 +3348,10 @@
         <v>21.4</v>
       </c>
       <c r="AB16" t="n">
-        <v>99.5</v>
+        <v>99.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>-1.5</v>
+        <v>-1.8</v>
       </c>
       <c r="AD16" t="n">
         <v>4</v>
@@ -3299,16 +3366,16 @@
         <v>11</v>
       </c>
       <c r="AH16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ16" t="n">
         <v>23</v>
       </c>
       <c r="AK16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL16" t="n">
         <v>27</v>
@@ -3317,7 +3384,7 @@
         <v>26</v>
       </c>
       <c r="AN16" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AO16" t="n">
         <v>5</v>
@@ -3329,7 +3396,7 @@
         <v>11</v>
       </c>
       <c r="AR16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS16" t="n">
         <v>30</v>
@@ -3338,7 +3405,7 @@
         <v>27</v>
       </c>
       <c r="AU16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV16" t="n">
         <v>7</v>
@@ -3350,19 +3417,19 @@
         <v>20</v>
       </c>
       <c r="AY16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AZ16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB16" t="n">
         <v>24</v>
       </c>
       <c r="BC16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-4-2015-16</t>
+          <t>2016-04-04</t>
         </is>
       </c>
     </row>
@@ -3391,55 +3458,55 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E17" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F17" t="n">
         <v>32</v>
       </c>
       <c r="G17" t="n">
-        <v>0.573</v>
+        <v>0.579</v>
       </c>
       <c r="H17" t="n">
         <v>48.4</v>
       </c>
       <c r="I17" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J17" t="n">
-        <v>81.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="K17" t="n">
         <v>0.469</v>
       </c>
       <c r="L17" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="M17" t="n">
         <v>18</v>
       </c>
       <c r="N17" t="n">
-        <v>0.333</v>
+        <v>0.337</v>
       </c>
       <c r="O17" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="P17" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.741</v>
+        <v>0.744</v>
       </c>
       <c r="R17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S17" t="n">
         <v>34.4</v>
       </c>
       <c r="T17" t="n">
-        <v>44.2</v>
+        <v>44.1</v>
       </c>
       <c r="U17" t="n">
         <v>21</v>
@@ -3457,40 +3524,40 @@
         <v>4.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>99.59999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AE17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG17" t="n">
         <v>9</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>10</v>
       </c>
       <c r="AH17" t="n">
         <v>10</v>
       </c>
       <c r="AI17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ17" t="n">
         <v>27</v>
       </c>
       <c r="AK17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL17" t="n">
         <v>28</v>
@@ -3499,16 +3566,16 @@
         <v>27</v>
       </c>
       <c r="AN17" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AO17" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AP17" t="n">
         <v>12</v>
       </c>
       <c r="AQ17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR17" t="n">
         <v>22</v>
@@ -3526,16 +3593,16 @@
         <v>15</v>
       </c>
       <c r="AW17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX17" t="n">
         <v>1</v>
       </c>
       <c r="AY17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ17" t="n">
         <v>4</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>3</v>
       </c>
       <c r="BA17" t="n">
         <v>19</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-4-2015-16</t>
+          <t>2016-04-04</t>
         </is>
       </c>
     </row>
@@ -3573,58 +3640,58 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E18" t="n">
         <v>32</v>
       </c>
       <c r="F18" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G18" t="n">
-        <v>0.421</v>
+        <v>0.416</v>
       </c>
       <c r="H18" t="n">
         <v>48.3</v>
       </c>
       <c r="I18" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="J18" t="n">
         <v>82</v>
       </c>
       <c r="K18" t="n">
-        <v>0.469</v>
+        <v>0.467</v>
       </c>
       <c r="L18" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="M18" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="N18" t="n">
-        <v>0.346</v>
+        <v>0.348</v>
       </c>
       <c r="O18" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="P18" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.745</v>
+        <v>0.747</v>
       </c>
       <c r="R18" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="S18" t="n">
         <v>31</v>
       </c>
       <c r="T18" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
       <c r="U18" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="V18" t="n">
         <v>15</v>
@@ -3639,16 +3706,16 @@
         <v>5.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>99.2</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC18" t="n">
-        <v>-3.4</v>
+        <v>-3.7</v>
       </c>
       <c r="AD18" t="n">
         <v>4</v>
@@ -3672,7 +3739,7 @@
         <v>26</v>
       </c>
       <c r="AK18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL18" t="n">
         <v>30</v>
@@ -3681,7 +3748,7 @@
         <v>30</v>
       </c>
       <c r="AN18" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AO18" t="n">
         <v>20</v>
@@ -3690,7 +3757,7 @@
         <v>18</v>
       </c>
       <c r="AQ18" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AR18" t="n">
         <v>14</v>
@@ -3699,16 +3766,16 @@
         <v>29</v>
       </c>
       <c r="AT18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU18" t="n">
         <v>8</v>
       </c>
       <c r="AV18" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AW18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX18" t="n">
         <v>6</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-4-2015-16</t>
+          <t>2016-04-04</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F19" t="n">
         <v>52</v>
       </c>
       <c r="G19" t="n">
-        <v>0.316</v>
+        <v>0.325</v>
       </c>
       <c r="H19" t="n">
         <v>48.5</v>
@@ -3773,7 +3840,7 @@
         <v>37.4</v>
       </c>
       <c r="J19" t="n">
-        <v>81.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="K19" t="n">
         <v>0.461</v>
@@ -3782,19 +3849,19 @@
         <v>5.4</v>
       </c>
       <c r="M19" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0.333</v>
+        <v>0.331</v>
       </c>
       <c r="O19" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="P19" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.794</v>
+        <v>0.795</v>
       </c>
       <c r="R19" t="n">
         <v>10.1</v>
@@ -3803,7 +3870,7 @@
         <v>31.6</v>
       </c>
       <c r="T19" t="n">
-        <v>41.7</v>
+        <v>41.6</v>
       </c>
       <c r="U19" t="n">
         <v>23</v>
@@ -3821,16 +3888,16 @@
         <v>5.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>101.3</v>
+        <v>101.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>-4.2</v>
+        <v>-4.1</v>
       </c>
       <c r="AD19" t="n">
         <v>4</v>
@@ -3845,10 +3912,10 @@
         <v>26</v>
       </c>
       <c r="AH19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ19" t="n">
         <v>29</v>
@@ -3887,7 +3954,7 @@
         <v>9</v>
       </c>
       <c r="AV19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW19" t="n">
         <v>16</v>
@@ -3896,10 +3963,10 @@
         <v>19</v>
       </c>
       <c r="AY19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ19" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA19" t="n">
         <v>7</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-4-2015-16</t>
+          <t>2016-04-04</t>
         </is>
       </c>
     </row>
@@ -3937,28 +4004,28 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E20" t="n">
         <v>29</v>
       </c>
       <c r="F20" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G20" t="n">
-        <v>0.392</v>
+        <v>0.382</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>38.5</v>
+        <v>38.4</v>
       </c>
       <c r="J20" t="n">
-        <v>85.90000000000001</v>
+        <v>86</v>
       </c>
       <c r="K20" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L20" t="n">
         <v>8.5</v>
@@ -3967,7 +4034,7 @@
         <v>23.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0.358</v>
+        <v>0.357</v>
       </c>
       <c r="O20" t="n">
         <v>17.3</v>
@@ -3976,22 +4043,22 @@
         <v>22.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.778</v>
+        <v>0.775</v>
       </c>
       <c r="R20" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="S20" t="n">
-        <v>33.4</v>
+        <v>33.3</v>
       </c>
       <c r="T20" t="n">
-        <v>42.9</v>
+        <v>42.7</v>
       </c>
       <c r="U20" t="n">
         <v>22</v>
       </c>
       <c r="V20" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="W20" t="n">
         <v>7.8</v>
@@ -4006,37 +4073,37 @@
         <v>20.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>102.8</v>
+        <v>102.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>-2.7</v>
+        <v>-3.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AE20" t="n">
         <v>25</v>
       </c>
       <c r="AF20" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AG20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AH20" t="n">
         <v>22</v>
       </c>
       <c r="AI20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ20" t="n">
         <v>8</v>
       </c>
       <c r="AK20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL20" t="n">
         <v>15</v>
@@ -4045,16 +4112,16 @@
         <v>15</v>
       </c>
       <c r="AN20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO20" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AP20" t="n">
         <v>22</v>
       </c>
       <c r="AQ20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR20" t="n">
         <v>23</v>
@@ -4063,7 +4130,7 @@
         <v>16</v>
       </c>
       <c r="AT20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU20" t="n">
         <v>17</v>
@@ -4075,10 +4142,10 @@
         <v>15</v>
       </c>
       <c r="AX20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ20" t="n">
         <v>20</v>
@@ -4087,10 +4154,10 @@
         <v>20</v>
       </c>
       <c r="BB20" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BC20" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-4-2015-16</t>
+          <t>2016-04-04</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E21" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F21" t="n">
         <v>47</v>
       </c>
       <c r="G21" t="n">
-        <v>0.39</v>
+        <v>0.397</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
@@ -4137,7 +4204,7 @@
         <v>36.8</v>
       </c>
       <c r="J21" t="n">
-        <v>83.8</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K21" t="n">
         <v>0.439</v>
@@ -4149,76 +4216,76 @@
         <v>21.4</v>
       </c>
       <c r="N21" t="n">
-        <v>0.345</v>
+        <v>0.346</v>
       </c>
       <c r="O21" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="P21" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="Q21" t="n">
         <v>0.806</v>
       </c>
       <c r="R21" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S21" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="T21" t="n">
-        <v>44.2</v>
+        <v>44.3</v>
       </c>
       <c r="U21" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="V21" t="n">
         <v>13.4</v>
       </c>
       <c r="W21" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="X21" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Y21" t="n">
         <v>4.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AA21" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>98.2</v>
+        <v>98.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>-2.9</v>
+        <v>-2.6</v>
       </c>
       <c r="AD21" t="n">
         <v>1</v>
       </c>
       <c r="AE21" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF21" t="n">
         <v>24</v>
       </c>
-      <c r="AF21" t="n">
-        <v>25</v>
-      </c>
       <c r="AG21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH21" t="n">
         <v>20</v>
       </c>
       <c r="AI21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ21" t="n">
         <v>19</v>
       </c>
       <c r="AK21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL21" t="n">
         <v>24</v>
@@ -4230,7 +4297,7 @@
         <v>20</v>
       </c>
       <c r="AO21" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AP21" t="n">
         <v>25</v>
@@ -4239,16 +4306,16 @@
         <v>1</v>
       </c>
       <c r="AR21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AS21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AT21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV21" t="n">
         <v>8</v>
@@ -4266,13 +4333,13 @@
         <v>9</v>
       </c>
       <c r="BA21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-4-2015-16</t>
+          <t>2016-04-04</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E22" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F22" t="n">
         <v>24</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
@@ -4328,7 +4395,7 @@
         <v>8.1</v>
       </c>
       <c r="M22" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="N22" t="n">
         <v>0.347</v>
@@ -4340,7 +4407,7 @@
         <v>25.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.785</v>
+        <v>0.787</v>
       </c>
       <c r="R22" t="n">
         <v>12.9</v>
@@ -4367,7 +4434,7 @@
         <v>4.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AA22" t="n">
         <v>20.1</v>
@@ -4397,7 +4464,7 @@
         <v>2</v>
       </c>
       <c r="AJ22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK22" t="n">
         <v>3</v>
@@ -4409,7 +4476,7 @@
         <v>18</v>
       </c>
       <c r="AN22" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AO22" t="n">
         <v>4</v>
@@ -4418,19 +4485,19 @@
         <v>7</v>
       </c>
       <c r="AQ22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR22" t="n">
         <v>1</v>
       </c>
       <c r="AS22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT22" t="n">
         <v>1</v>
       </c>
       <c r="AU22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV22" t="n">
         <v>26</v>
@@ -4439,16 +4506,16 @@
         <v>21</v>
       </c>
       <c r="AX22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY22" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AZ22" t="n">
         <v>16</v>
       </c>
       <c r="BA22" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BB22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-4-2015-16</t>
+          <t>2016-04-04</t>
         </is>
       </c>
     </row>
@@ -4483,55 +4550,55 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E23" t="n">
         <v>33</v>
       </c>
       <c r="F23" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G23" t="n">
-        <v>0.434</v>
+        <v>0.429</v>
       </c>
       <c r="H23" t="n">
         <v>48.6</v>
       </c>
       <c r="I23" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="J23" t="n">
-        <v>86.7</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L23" t="n">
         <v>7.9</v>
       </c>
       <c r="M23" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0.353</v>
+        <v>0.351</v>
       </c>
       <c r="O23" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="P23" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.762</v>
+        <v>0.761</v>
       </c>
       <c r="R23" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="S23" t="n">
-        <v>33.1</v>
+        <v>33.2</v>
       </c>
       <c r="T23" t="n">
-        <v>43.4</v>
+        <v>43.6</v>
       </c>
       <c r="U23" t="n">
         <v>23.6</v>
@@ -4546,7 +4613,7 @@
         <v>5</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z23" t="n">
         <v>20.9</v>
@@ -4555,7 +4622,7 @@
         <v>18.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>102.1</v>
+        <v>101.9</v>
       </c>
       <c r="AC23" t="n">
         <v>-1.4</v>
@@ -4573,13 +4640,13 @@
         <v>20</v>
       </c>
       <c r="AH23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI23" t="n">
         <v>5</v>
       </c>
       <c r="AJ23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK23" t="n">
         <v>13</v>
@@ -4600,10 +4667,10 @@
         <v>30</v>
       </c>
       <c r="AQ23" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AR23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS23" t="n">
         <v>17</v>
@@ -4627,7 +4694,7 @@
         <v>23</v>
       </c>
       <c r="AZ23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA23" t="n">
         <v>29</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-4-2015-16</t>
+          <t>2016-04-04</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E24" t="n">
         <v>9</v>
       </c>
       <c r="F24" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G24" t="n">
-        <v>0.118</v>
+        <v>0.117</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
@@ -4701,10 +4768,10 @@
         <v>15.6</v>
       </c>
       <c r="P24" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.695</v>
       </c>
       <c r="R24" t="n">
         <v>9.4</v>
@@ -4713,10 +4780,10 @@
         <v>31.9</v>
       </c>
       <c r="T24" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="U24" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="V24" t="n">
         <v>16.6</v>
@@ -4728,7 +4795,7 @@
         <v>6</v>
       </c>
       <c r="Y24" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Z24" t="n">
         <v>21.9</v>
@@ -4740,7 +4807,7 @@
         <v>97</v>
       </c>
       <c r="AC24" t="n">
-        <v>-10.4</v>
+        <v>-10.5</v>
       </c>
       <c r="AD24" t="n">
         <v>4</v>
@@ -4761,19 +4828,19 @@
         <v>28</v>
       </c>
       <c r="AJ24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK24" t="n">
         <v>29</v>
       </c>
       <c r="AL24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM24" t="n">
         <v>9</v>
       </c>
       <c r="AN24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO24" t="n">
         <v>29</v>
@@ -4785,7 +4852,7 @@
         <v>29</v>
       </c>
       <c r="AR24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS24" t="n">
         <v>26</v>
@@ -4794,22 +4861,22 @@
         <v>30</v>
       </c>
       <c r="AU24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV24" t="n">
         <v>29</v>
       </c>
       <c r="AW24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX24" t="n">
         <v>3</v>
       </c>
       <c r="AY24" t="n">
+        <v>28</v>
+      </c>
+      <c r="AZ24" t="n">
         <v>27</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>26</v>
       </c>
       <c r="BA24" t="n">
         <v>25</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-4-2015-16</t>
+          <t>2016-04-04</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E25" t="n">
         <v>20</v>
       </c>
       <c r="F25" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G25" t="n">
-        <v>0.263</v>
+        <v>0.26</v>
       </c>
       <c r="H25" t="n">
         <v>48.1</v>
@@ -4868,7 +4935,7 @@
         <v>85.2</v>
       </c>
       <c r="K25" t="n">
-        <v>0.435</v>
+        <v>0.434</v>
       </c>
       <c r="L25" t="n">
         <v>9</v>
@@ -4877,28 +4944,28 @@
         <v>25.8</v>
       </c>
       <c r="N25" t="n">
-        <v>0.35</v>
+        <v>0.349</v>
       </c>
       <c r="O25" t="n">
         <v>17.3</v>
       </c>
       <c r="P25" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.753</v>
+        <v>0.751</v>
       </c>
       <c r="R25" t="n">
         <v>11.2</v>
       </c>
       <c r="S25" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="T25" t="n">
-        <v>44.3</v>
+        <v>44.4</v>
       </c>
       <c r="U25" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V25" t="n">
         <v>17</v>
@@ -4913,16 +4980,16 @@
         <v>5.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AB25" t="n">
         <v>100.3</v>
       </c>
       <c r="AC25" t="n">
-        <v>-7.3</v>
+        <v>-7.4</v>
       </c>
       <c r="AD25" t="n">
         <v>4</v>
@@ -4958,10 +5025,10 @@
         <v>15</v>
       </c>
       <c r="AO25" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AP25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ25" t="n">
         <v>19</v>
@@ -4973,10 +5040,10 @@
         <v>18</v>
       </c>
       <c r="AT25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AU25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV25" t="n">
         <v>30</v>
@@ -4988,7 +5055,7 @@
         <v>27</v>
       </c>
       <c r="AY25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ25" t="n">
         <v>30</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-4-2015-16</t>
+          <t>2016-04-04</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E26" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F26" t="n">
         <v>37</v>
       </c>
       <c r="G26" t="n">
-        <v>0.519</v>
+        <v>0.526</v>
       </c>
       <c r="H26" t="n">
         <v>48.3</v>
@@ -5050,37 +5117,37 @@
         <v>85.8</v>
       </c>
       <c r="K26" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L26" t="n">
         <v>10.5</v>
       </c>
       <c r="M26" t="n">
-        <v>28.3</v>
+        <v>28.4</v>
       </c>
       <c r="N26" t="n">
         <v>0.369</v>
       </c>
       <c r="O26" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="P26" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.749</v>
+        <v>0.75</v>
       </c>
       <c r="R26" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S26" t="n">
-        <v>34</v>
+        <v>34.2</v>
       </c>
       <c r="T26" t="n">
         <v>45.6</v>
       </c>
       <c r="U26" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V26" t="n">
         <v>14.6</v>
@@ -5101,16 +5168,16 @@
         <v>19.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>104.7</v>
+        <v>104.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="AD26" t="n">
         <v>1</v>
       </c>
       <c r="AE26" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AF26" t="n">
         <v>14</v>
@@ -5122,34 +5189,34 @@
         <v>20</v>
       </c>
       <c r="AI26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ26" t="n">
         <v>9</v>
       </c>
       <c r="AK26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL26" t="n">
         <v>5</v>
       </c>
       <c r="AM26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN26" t="n">
         <v>4</v>
       </c>
       <c r="AO26" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AP26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ26" t="n">
         <v>20</v>
       </c>
       <c r="AR26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS26" t="n">
         <v>7</v>
@@ -5158,13 +5225,13 @@
         <v>5</v>
       </c>
       <c r="AU26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV26" t="n">
         <v>17</v>
       </c>
       <c r="AW26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX26" t="n">
         <v>18</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-4-2015-16</t>
+          <t>2016-04-04</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E27" t="n">
         <v>31</v>
       </c>
       <c r="F27" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G27" t="n">
-        <v>0.408</v>
+        <v>0.403</v>
       </c>
       <c r="H27" t="n">
         <v>48.3</v>
@@ -5229,43 +5296,43 @@
         <v>40.1</v>
       </c>
       <c r="J27" t="n">
-        <v>86.2</v>
+        <v>86.3</v>
       </c>
       <c r="K27" t="n">
         <v>0.465</v>
       </c>
       <c r="L27" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="M27" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="N27" t="n">
-        <v>0.356</v>
+        <v>0.358</v>
       </c>
       <c r="O27" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="P27" t="n">
-        <v>25.9</v>
+        <v>25.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.73</v>
+        <v>0.729</v>
       </c>
       <c r="R27" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="S27" t="n">
         <v>33.8</v>
       </c>
       <c r="T27" t="n">
-        <v>44.3</v>
+        <v>44.4</v>
       </c>
       <c r="U27" t="n">
         <v>24.7</v>
       </c>
       <c r="V27" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="W27" t="n">
         <v>8.9</v>
@@ -5277,7 +5344,7 @@
         <v>5.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AA27" t="n">
         <v>22.1</v>
@@ -5286,19 +5353,19 @@
         <v>107</v>
       </c>
       <c r="AC27" t="n">
-        <v>-2</v>
+        <v>-2.1</v>
       </c>
       <c r="AD27" t="n">
         <v>4</v>
       </c>
       <c r="AE27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF27" t="n">
         <v>22</v>
       </c>
       <c r="AG27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH27" t="n">
         <v>17</v>
@@ -5307,7 +5374,7 @@
         <v>4</v>
       </c>
       <c r="AJ27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK27" t="n">
         <v>6</v>
@@ -5319,7 +5386,7 @@
         <v>22</v>
       </c>
       <c r="AN27" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AO27" t="n">
         <v>7</v>
@@ -5334,7 +5401,7 @@
         <v>13</v>
       </c>
       <c r="AS27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT27" t="n">
         <v>9</v>
@@ -5349,16 +5416,16 @@
         <v>5</v>
       </c>
       <c r="AX27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AZ27" t="n">
         <v>13</v>
       </c>
       <c r="BA27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB27" t="n">
         <v>3</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-4-2015-16</t>
+          <t>2016-04-04</t>
         </is>
       </c>
     </row>
@@ -5393,25 +5460,25 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E28" t="n">
         <v>64</v>
       </c>
       <c r="F28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G28" t="n">
-        <v>0.853</v>
+        <v>0.842</v>
       </c>
       <c r="H28" t="n">
         <v>48</v>
       </c>
       <c r="I28" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="J28" t="n">
-        <v>82.90000000000001</v>
+        <v>83</v>
       </c>
       <c r="K28" t="n">
         <v>0.488</v>
@@ -5420,40 +5487,40 @@
         <v>7.1</v>
       </c>
       <c r="M28" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="N28" t="n">
-        <v>0.382</v>
+        <v>0.381</v>
       </c>
       <c r="O28" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="P28" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.804</v>
+        <v>0.805</v>
       </c>
       <c r="R28" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="S28" t="n">
-        <v>34.8</v>
+        <v>34.7</v>
       </c>
       <c r="T28" t="n">
-        <v>44.3</v>
+        <v>44.1</v>
       </c>
       <c r="U28" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="V28" t="n">
         <v>13.2</v>
       </c>
       <c r="W28" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X28" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Y28" t="n">
         <v>3.8</v>
@@ -5468,10 +5535,10 @@
         <v>104.2</v>
       </c>
       <c r="AC28" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
@@ -5492,7 +5559,7 @@
         <v>24</v>
       </c>
       <c r="AK28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL28" t="n">
         <v>25</v>
@@ -5513,25 +5580,25 @@
         <v>2</v>
       </c>
       <c r="AR28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS28" t="n">
         <v>5</v>
       </c>
       <c r="AT28" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AU28" t="n">
         <v>3</v>
       </c>
       <c r="AV28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW28" t="n">
         <v>13</v>
       </c>
       <c r="AX28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY28" t="n">
         <v>2</v>
@@ -5543,7 +5610,7 @@
         <v>23</v>
       </c>
       <c r="BB28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-4-2015-16</t>
+          <t>2016-04-04</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E29" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F29" t="n">
         <v>25</v>
       </c>
       <c r="G29" t="n">
-        <v>0.667</v>
+        <v>0.671</v>
       </c>
       <c r="H29" t="n">
         <v>48.3</v>
@@ -5608,34 +5675,34 @@
         <v>0.37</v>
       </c>
       <c r="O29" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="P29" t="n">
-        <v>26.8</v>
+        <v>26.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.784</v>
+        <v>0.782</v>
       </c>
       <c r="R29" t="n">
         <v>10.2</v>
       </c>
       <c r="S29" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="T29" t="n">
-        <v>43.1</v>
+        <v>43.2</v>
       </c>
       <c r="U29" t="n">
         <v>18.6</v>
       </c>
       <c r="V29" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="W29" t="n">
         <v>7.8</v>
       </c>
       <c r="X29" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y29" t="n">
         <v>5.3</v>
@@ -5644,16 +5711,16 @@
         <v>19.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>102.7</v>
+        <v>102.8</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AE29" t="n">
         <v>5</v>
@@ -5665,7 +5732,7 @@
         <v>5</v>
       </c>
       <c r="AH29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI29" t="n">
         <v>27</v>
@@ -5695,7 +5762,7 @@
         <v>10</v>
       </c>
       <c r="AR29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS29" t="n">
         <v>21</v>
@@ -5707,7 +5774,7 @@
         <v>29</v>
       </c>
       <c r="AV29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW29" t="n">
         <v>14</v>
@@ -5716,13 +5783,13 @@
         <v>11</v>
       </c>
       <c r="AY29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ29" t="n">
         <v>10</v>
       </c>
       <c r="BA29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB29" t="n">
         <v>14</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-4-2015-16</t>
+          <t>2016-04-04</t>
         </is>
       </c>
     </row>
@@ -5757,19 +5824,19 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E30" t="n">
         <v>39</v>
       </c>
       <c r="F30" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G30" t="n">
-        <v>0.513</v>
+        <v>0.506</v>
       </c>
       <c r="H30" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="I30" t="n">
         <v>36.1</v>
@@ -5781,13 +5848,13 @@
         <v>0.448</v>
       </c>
       <c r="L30" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="M30" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="N30" t="n">
-        <v>0.358</v>
+        <v>0.357</v>
       </c>
       <c r="O30" t="n">
         <v>17.3</v>
@@ -5799,13 +5866,13 @@
         <v>0.745</v>
       </c>
       <c r="R30" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="S30" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="T30" t="n">
-        <v>43.4</v>
+        <v>43.3</v>
       </c>
       <c r="U30" t="n">
         <v>19</v>
@@ -5823,25 +5890,25 @@
         <v>4.8</v>
       </c>
       <c r="Z30" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AA30" t="n">
         <v>20</v>
       </c>
       <c r="AB30" t="n">
-        <v>98</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC30" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AD30" t="n">
         <v>4</v>
       </c>
       <c r="AE30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG30" t="n">
         <v>15</v>
@@ -5856,28 +5923,28 @@
         <v>30</v>
       </c>
       <c r="AK30" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AL30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN30" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AO30" t="n">
         <v>17</v>
       </c>
       <c r="AP30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ30" t="n">
         <v>22</v>
       </c>
       <c r="AR30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS30" t="n">
         <v>23</v>
@@ -5889,10 +5956,10 @@
         <v>28</v>
       </c>
       <c r="AV30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX30" t="n">
         <v>13</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-4-2015-16</t>
+          <t>2016-04-04</t>
         </is>
       </c>
     </row>
@@ -5939,37 +6006,37 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E31" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F31" t="n">
         <v>40</v>
       </c>
       <c r="G31" t="n">
-        <v>0.474</v>
+        <v>0.481</v>
       </c>
       <c r="H31" t="n">
         <v>48.2</v>
       </c>
       <c r="I31" t="n">
-        <v>39.3</v>
+        <v>39.2</v>
       </c>
       <c r="J31" t="n">
-        <v>85.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L31" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="M31" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="N31" t="n">
-        <v>0.36</v>
+        <v>0.359</v>
       </c>
       <c r="O31" t="n">
         <v>16.4</v>
@@ -5978,25 +6045,25 @@
         <v>22.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.733</v>
+        <v>0.731</v>
       </c>
       <c r="R31" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="S31" t="n">
         <v>32.5</v>
       </c>
       <c r="T31" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
       <c r="U31" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="V31" t="n">
         <v>14.5</v>
       </c>
       <c r="W31" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="X31" t="n">
         <v>3.9</v>
@@ -6005,13 +6072,13 @@
         <v>4.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AA31" t="n">
         <v>20.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>103.7</v>
+        <v>103.5</v>
       </c>
       <c r="AC31" t="n">
         <v>-1.1</v>
@@ -6032,13 +6099,13 @@
         <v>26</v>
       </c>
       <c r="AI31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ31" t="n">
         <v>10</v>
       </c>
       <c r="AK31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL31" t="n">
         <v>13</v>
@@ -6047,19 +6114,19 @@
         <v>14</v>
       </c>
       <c r="AN31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ31" t="n">
         <v>25</v>
       </c>
       <c r="AR31" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AS31" t="n">
         <v>22</v>
@@ -6077,13 +6144,13 @@
         <v>7</v>
       </c>
       <c r="AX31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY31" t="n">
         <v>6</v>
       </c>
       <c r="AZ31" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="BA31" t="n">
         <v>15</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-4-2015-16</t>
+          <t>2016-04-04</t>
         </is>
       </c>
     </row>
